--- a/VerveStacks_FRA_grids_kan25/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_FRA_grids_kan25\SubRES_Tmpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\assumptions\VerveStacks_ISO_template\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFA3C06-AB26-48C6-90B1-FC0CC294D76E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253B7126-F1B2-4F6B-AB53-4221FBC2A220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DC details" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="79">
   <si>
     <t>process</t>
   </si>
@@ -123,6 +123,156 @@
   </si>
   <si>
     <t>~tfm_ins-TS: attribute=NCAP_PASTI</t>
+  </si>
+  <si>
+    <t>e_w110086345-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/110086345-400 (Nimes, 30 km)</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/111558550-400 (Bayonne, 9 km)</t>
+  </si>
+  <si>
+    <t>e_w112342683-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/112342683-400 (Nantes, 25 km)</t>
+  </si>
+  <si>
+    <t>e_w118086309-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/118086309-400 (Strasbourg, 16 km)</t>
+  </si>
+  <si>
+    <t>e_w146695955-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/146695955-400 (Brest, 23 km)</t>
+  </si>
+  <si>
+    <t>e_w147132694-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/147132694-400 (Grenoble, 26 km)</t>
+  </si>
+  <si>
+    <t>e_w159167277-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/159167277-400 (Besancon, 42 km)</t>
+  </si>
+  <si>
+    <t>e_w179260933-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/179260933-400 (Dijon, 25 km)</t>
+  </si>
+  <si>
+    <t>e_w235370803-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/235370803-400 (Bordeaux, 28 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/24020601-400 (Lyon, 24 km)</t>
+  </si>
+  <si>
+    <t>e_w27259817-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/27259817-400 (Marseille, 17 km)</t>
+  </si>
+  <si>
+    <t>e_w36805588-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/36805588-400 (Amiens, 6 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/49510896-400 (Toulouse, 27 km)</t>
+  </si>
+  <si>
+    <t>e_w71933077-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/71933077-400 (Clermont-Ferrand, 15 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/79866837-400 (Paris, 64 km)</t>
+  </si>
+  <si>
+    <t>e_w81641090-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/81641090-400 (Metz, 11 km)</t>
+  </si>
+  <si>
+    <t>e_w82599261-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/82599261-400 (Troyes, 27 km)</t>
+  </si>
+  <si>
+    <t>e_w82825438-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/82825438-400 (Reims, 74 km)</t>
+  </si>
+  <si>
+    <t>e_w85047359-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/85047359-400 (Paris, 41 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/85203486-400 (Dunkerque, 18 km)</t>
+  </si>
+  <si>
+    <t>e_w85605950-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/85605950-400 (Lille, 12 km)</t>
+  </si>
+  <si>
+    <t>e_w85710783-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/85710783-400 (Rouen, 24 km)</t>
+  </si>
+  <si>
+    <t>e_w85995894-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/85995894-400 (Rennes, 9 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/90842395-400 (Nice, 13 km)</t>
+  </si>
+  <si>
+    <t>e_w98890904-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/98890904-400 (Beziers, 45 km)</t>
+  </si>
+  <si>
+    <t>e_w99722046-400_FRA</t>
+  </si>
+  <si>
+    <t>grid node -- way/99722046-400 (Angers, 44 km)</t>
+  </si>
+  <si>
+    <t>node</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>include</t>
   </si>
 </sst>
 </file>
@@ -542,329 +692,527 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="C2:R26"/>
+  <dimension ref="A1:T27"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.73046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.86328125" customWidth="1"/>
-    <col min="9" max="16" width="4.73046875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.53125" customWidth="1"/>
-    <col min="21" max="21" width="4.73046875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.46484375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.73046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.9296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.73046875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.46484375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.53125" customWidth="1"/>
+    <col min="23" max="23" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.46484375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:16">
-      <c r="D2" t="s">
+    <row r="1" spans="1:18">
+      <c r="A1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>4</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="3:16">
-      <c r="D3" t="s">
+    <row r="3" spans="1:18">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>5</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>22</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>24</v>
       </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="3:16">
-      <c r="D4" t="s">
+    <row r="4" spans="1:18">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>8</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
         <v>23</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>8.76</v>
       </c>
-      <c r="J4" t="s">
+      <c r="L4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="3:16">
-      <c r="D5" t="s">
+    <row r="5" spans="1:18">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>10</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>26</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>1</v>
       </c>
-      <c r="J5" t="s">
+      <c r="L5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="3:16">
-      <c r="D6" t="s">
+    <row r="6" spans="1:18">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
         <v>13</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="3:16">
-      <c r="C10" t="s">
+    <row r="7" spans="1:18">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
         <v>14</v>
       </c>
-      <c r="H10" t="s">
+      <c r="J10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="3:16">
-      <c r="C11" t="s">
+    <row r="11" spans="1:18">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
         <v>0</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>2</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>1</v>
       </c>
-      <c r="H11" t="s">
+      <c r="J11" t="s">
         <v>0</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>2025</v>
       </c>
-      <c r="J11">
-        <f>I11+1</f>
+      <c r="L11">
+        <f>K11+1</f>
         <v>2026</v>
       </c>
-      <c r="K11">
-        <f t="shared" ref="K11:N11" si="0">J11+1</f>
+      <c r="M11">
+        <f t="shared" ref="M11:P11" si="0">L11+1</f>
         <v>2027</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <f t="shared" si="0"/>
         <v>2028</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="N11">
+      <c r="P11">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
-      <c r="O11">
+      <c r="Q11">
         <v>2032</v>
       </c>
-      <c r="P11">
+      <c r="R11">
         <v>2035</v>
       </c>
     </row>
-    <row r="12" spans="3:16">
-      <c r="C12" t="s">
+    <row r="12" spans="1:18">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" t="s">
         <v>15</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>3</v>
       </c>
-      <c r="E12" t="str">
-        <f>E2</f>
+      <c r="G12" t="str">
+        <f>G2</f>
         <v>e_w79866837-400_FRA</v>
       </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
         <v>15</v>
-      </c>
-      <c r="J12">
-        <v>0.5</v>
       </c>
       <c r="L12">
         <v>0.5</v>
       </c>
       <c r="N12">
+        <v>0.5</v>
+      </c>
+      <c r="P12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="3:16">
-      <c r="C13" t="s">
+    <row r="13" spans="1:18">
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" t="s">
         <v>16</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>3</v>
       </c>
-      <c r="E13" t="str">
-        <f>E3</f>
+      <c r="G13" t="str">
+        <f>G3</f>
         <v>e_w85203486-400_FRA</v>
       </c>
-      <c r="H13" t="s">
+      <c r="J13" t="s">
         <v>16</v>
-      </c>
-      <c r="K13">
-        <v>0.5</v>
       </c>
       <c r="M13">
         <v>0.5</v>
       </c>
       <c r="O13">
+        <v>0.5</v>
+      </c>
+      <c r="Q13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="3:16">
-      <c r="C14" t="s">
+    <row r="14" spans="1:18">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" t="s">
         <v>17</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>3</v>
       </c>
-      <c r="E14" t="str">
-        <f>E4</f>
+      <c r="G14" t="str">
+        <f>G4</f>
         <v>e_w49510896-400_FRA</v>
       </c>
-      <c r="H14" t="s">
+      <c r="J14" t="s">
         <v>17</v>
       </c>
-      <c r="K14">
+      <c r="M14">
         <v>1</v>
       </c>
-      <c r="N14">
+      <c r="P14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="3:16">
-      <c r="C15" t="s">
+    <row r="15" spans="1:18">
+      <c r="A15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" t="s">
         <v>18</v>
       </c>
-      <c r="D15" t="s">
+      <c r="F15" t="s">
         <v>3</v>
       </c>
-      <c r="E15" t="str">
-        <f>E5</f>
+      <c r="G15" t="str">
+        <f>G5</f>
         <v>e_w24020601-400_FRA</v>
       </c>
-      <c r="H15" t="s">
+      <c r="J15" t="s">
         <v>18</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>0.25</v>
       </c>
-      <c r="K15">
+      <c r="M15">
         <v>0.25</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="3:16">
-      <c r="C16" t="s">
+    <row r="16" spans="1:18">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
         <v>19</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>3</v>
       </c>
-      <c r="E16" t="str">
-        <f>E6</f>
+      <c r="G16" t="str">
+        <f>G6</f>
         <v>e_w90842395-400_FRA</v>
       </c>
-      <c r="H16" t="s">
+      <c r="J16" t="s">
         <v>19</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="8:18">
-      <c r="Q18" s="1">
-        <f>SUM(I12:Q16)</f>
+    <row r="17" spans="1:20">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="S18" s="1">
+        <f>SUM(K12:S16)</f>
         <v>8</v>
       </c>
-      <c r="R18" s="2" t="s">
+      <c r="T18" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="8:18">
-      <c r="H20" t="s">
+    <row r="19" spans="1:20">
+      <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="A20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J20" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="8:18">
-      <c r="H21" t="s">
+    <row r="21" spans="1:20">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="J21" t="s">
         <v>0</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>2025</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="8:18">
-      <c r="H22" t="s">
+    <row r="22" spans="1:20">
+      <c r="A22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="J22" t="s">
         <v>15</v>
       </c>
-      <c r="I22">
+      <c r="K22">
         <v>0.85</v>
       </c>
-      <c r="J22">
+      <c r="L22">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="8:18">
-      <c r="H23" t="s">
+    <row r="23" spans="1:20">
+      <c r="A23" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" t="s">
+        <v>68</v>
+      </c>
+      <c r="J23" t="s">
         <v>16</v>
       </c>
-      <c r="I23">
+      <c r="K23">
         <v>0.85</v>
       </c>
-      <c r="J23">
+      <c r="L23">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="8:18">
-      <c r="H24" t="s">
+    <row r="24" spans="1:20">
+      <c r="A24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="J24" t="s">
         <v>17</v>
       </c>
-      <c r="I24">
+      <c r="K24">
         <v>0.85</v>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="8:18">
-      <c r="H25" t="s">
+    <row r="25" spans="1:20">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
+        <v>71</v>
+      </c>
+      <c r="J25" t="s">
         <v>18</v>
       </c>
-      <c r="I25">
+      <c r="K25">
         <v>0.85</v>
       </c>
-      <c r="J25">
+      <c r="L25">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="8:18">
-      <c r="H26" t="s">
+    <row r="26" spans="1:20">
+      <c r="A26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" t="s">
+        <v>73</v>
+      </c>
+      <c r="J26" t="s">
         <v>19</v>
       </c>
-      <c r="I26">
+      <c r="K26">
         <v>0.85</v>
       </c>
-      <c r="J26">
+      <c r="L26">
         <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20">
+      <c r="A27" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
